--- a/outputs/tables/tab2_paises.xlsx
+++ b/outputs/tables/tab2_paises.xlsx
@@ -357,7 +357,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="@"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="11"/>
@@ -421,19 +423,19 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FF888888"/>
       </bottom>
     </border>
     <border>
-      <bottom style="thin">
+      <top style="thin">
         <color rgb="FF888888"/>
-      </bottom>
+      </top>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -445,13 +447,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -900,16 +908,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1292,7 +1300,7 @@
       </c>
     </row>
     <row r="40" ht="116" customHeight="1">
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="10" t="s">
         <v>112</v>
       </c>
     </row>

--- a/outputs/tables/tab2_paises.xlsx
+++ b/outputs/tables/tab2_paises.xlsx
@@ -722,6 +722,9 @@
       <top style="medium">
         <color rgb="FF888888"/>
       </top>
+      <bottom style="medium">
+        <color rgb="FF888888"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">

--- a/outputs/tables/tab2_paises.xlsx
+++ b/outputs/tables/tab2_paises.xlsx
@@ -2431,7 +2431,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" ht="130" customHeight="1">
+    <row r="41" ht="125" customHeight="1">
       <c r="B41" s="9" t="s">
         <v>208</v>
       </c>
